--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6780"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="VWO Register Page" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="101">
   <si>
     <t>Test Case Template for Project</t>
   </si>
@@ -54,6 +54,9 @@
     <t>Created Date</t>
   </si>
   <si>
+    <t>15/4/2026</t>
+  </si>
+  <si>
     <t>Scenario TID</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
   </si>
   <si>
     <t xml:space="preserve">Executed QA Name </t>
+  </si>
+  <si>
+    <t>Screenshots</t>
   </si>
   <si>
     <t>VWO Register Page: Load Free Trial Page</t>
@@ -175,6 +181,9 @@
     <t>Afifa</t>
   </si>
   <si>
+    <t>SS01</t>
+  </si>
+  <si>
     <t>VWO Register Page: Submit Empty Email</t>
   </si>
   <si>
@@ -193,13 +202,16 @@
     <t>Error occured: 'A value for this field is required'</t>
   </si>
   <si>
+    <t>SS02</t>
+  </si>
+  <si>
     <t>VWO Register Page: Invalid email format</t>
   </si>
   <si>
     <t>TC03</t>
   </si>
   <si>
-    <t>1) Go to business email field               2) Enter a random text i.e abc                                    3) Click on 'Create a free trial account'</t>
+    <t>1) Go to business email field               2) Enter a random text                                     3) Click on 'Create a free trial account'</t>
   </si>
   <si>
     <t xml:space="preserve">An error should occur </t>
@@ -208,6 +220,9 @@
     <t>Error occured: 'The email address you entered is incorrect'</t>
   </si>
   <si>
+    <t>SS03</t>
+  </si>
+  <si>
     <t>VWO Register Page: Invalid email</t>
   </si>
   <si>
@@ -223,6 +238,9 @@
     <t>Error occured: 'gmail.com doesn't look like a business domain. Please use your business email'</t>
   </si>
   <si>
+    <t>SS04</t>
+  </si>
+  <si>
     <t>VWO Register Page: Valid email</t>
   </si>
   <si>
@@ -238,6 +256,9 @@
     <t>Form appeared asking for First name, Last name and Phone number</t>
   </si>
   <si>
+    <t>SS05</t>
+  </si>
+  <si>
     <t>VWO Register Page: Privacy &amp; Terms Checkbox</t>
   </si>
   <si>
@@ -253,111 +274,120 @@
     <t>Create a free trial account' button is disabled</t>
   </si>
   <si>
-    <t>VWO Register Page; Submit Credential form empty</t>
+    <t>SS06</t>
+  </si>
+  <si>
+    <t>VWO Register Page; Invalid input for text field</t>
   </si>
   <si>
     <t>TC07</t>
   </si>
   <si>
-    <t>1) Leave all the fields empty                 2) Click on 'Create an account'</t>
-  </si>
-  <si>
-    <t>Error occured: 'A value for this field is required' for all the fields</t>
-  </si>
-  <si>
-    <t>VWO Register Page; Invalid input for text field</t>
+    <t>1) Enter number in the name field                                                   2) Click on ' Create an account'</t>
+  </si>
+  <si>
+    <t>Name field should ask for valid text instead of numbers</t>
+  </si>
+  <si>
+    <t>Name fields are accepting numbers</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>SS07</t>
+  </si>
+  <si>
+    <t>VWO Register Page; Invalid input for number field</t>
   </si>
   <si>
     <t>TC08</t>
   </si>
   <si>
-    <t>1) Enter number in the name field                                                   2) Click on ' Create an account'</t>
-  </si>
-  <si>
-    <t>Name field should ask for valid text instead of numbers</t>
-  </si>
-  <si>
-    <t>Name fields are accepting numbers</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>VWO Register Page; Invalid input for number field</t>
+    <t>1) Enter text in the number field                                                   2) Click on ' Create an account'</t>
+  </si>
+  <si>
+    <t>Phone number  field should ask for numbers</t>
+  </si>
+  <si>
+    <t>Phone number field is showing an error: 'Please enter a valid phone number'</t>
+  </si>
+  <si>
+    <t>SS08</t>
+  </si>
+  <si>
+    <t>VWO Register Page; Credential form Privacy &amp; Terms Checkbox</t>
   </si>
   <si>
     <t>TC09</t>
   </si>
   <si>
-    <t>1) Enter text in the number field                                                   2) Click on ' Create an account'</t>
-  </si>
-  <si>
-    <t>Phone number  field should ask for numbers</t>
-  </si>
-  <si>
-    <t>Phone number field is showing an error: 'Please enter a valid phone number'</t>
-  </si>
-  <si>
-    <t>VWO Register Page; Credential form Privacy &amp; Terms Checkbox</t>
+    <t>1) Enter all the fields correctly                              2) Uncheck terms and conditions box                                                    3) Click on 'Create an account'</t>
+  </si>
+  <si>
+    <t>Create an account' button should be disabled</t>
+  </si>
+  <si>
+    <t>Create an account' button is disabled</t>
+  </si>
+  <si>
+    <t>SS09</t>
+  </si>
+  <si>
+    <t>VWO Register Page; Credential form Link navigation</t>
   </si>
   <si>
     <t>TC10</t>
   </si>
   <si>
-    <t>1) Enter all the fields correctly                              2) Uncheck terms and conditions box                                                    3) Click on 'Create an account'</t>
-  </si>
-  <si>
-    <t>Create an account' button should be disabled</t>
-  </si>
-  <si>
-    <t>Create an account' button is disabled</t>
-  </si>
-  <si>
-    <t>VWO Register Page; Credential form Link navigation</t>
+    <t>1) Click on Privacy Policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A new page should be opened or a dialogue box should apper </t>
+  </si>
+  <si>
+    <t>A new page is opened</t>
+  </si>
+  <si>
+    <t>SS10</t>
   </si>
   <si>
     <t>TC11</t>
   </si>
   <si>
-    <t>1) Click on Privacy Policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A new page should be opened or a dialogue box should apper </t>
-  </si>
-  <si>
-    <t>A new page is opened</t>
+    <t>1) Click on Terms</t>
+  </si>
+  <si>
+    <t>SS11</t>
+  </si>
+  <si>
+    <t>VWO Register Page; Credential form filled</t>
   </si>
   <si>
     <t>TC12</t>
   </si>
   <si>
-    <t>1) Click on Terms</t>
-  </si>
-  <si>
-    <t>VWO Register Page; Credential form filled</t>
+    <t>After valid submission</t>
+  </si>
+  <si>
+    <t>1) Enter all the valid credentials                                  2) Click on 'Create an Account"</t>
+  </si>
+  <si>
+    <t>Account created page shows up</t>
+  </si>
+  <si>
+    <t>Redirected to a new page saying 'Welcome'</t>
+  </si>
+  <si>
+    <t>SS12</t>
+  </si>
+  <si>
+    <t>VWO Register Page</t>
   </si>
   <si>
     <t>TC13</t>
   </si>
   <si>
-    <t>After valid submission</t>
-  </si>
-  <si>
-    <t>1) Enter all the valid credentials                                  2) Click on 'Create an Account"</t>
-  </si>
-  <si>
-    <t>Account created page shows up</t>
-  </si>
-  <si>
-    <t>Redirected to a new page saying 'Welcome'</t>
-  </si>
-  <si>
-    <t>VWO Register Page</t>
-  </si>
-  <si>
-    <t>TC14</t>
-  </si>
-  <si>
     <t>1) Enter an already usead email  2)Click on 'Create a free trial account'</t>
   </si>
   <si>
@@ -365,6 +395,9 @@
   </si>
   <si>
     <t>Error occured: 'An account with this email already exists.'</t>
+  </si>
+  <si>
+    <t>SS13</t>
   </si>
   <si>
     <t>Login Page</t>
@@ -380,7 +413,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="38">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -463,11 +496,35 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
       <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -487,6 +544,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
@@ -621,7 +685,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -648,12 +712,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF3F3F3"/>
         <bgColor rgb="FFF3F3F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.05"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
@@ -666,6 +754,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -799,12 +911,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -975,31 +1081,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1008,119 +1102,131 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1143,27 +1249,41 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1173,37 +1293,56 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,7 +1358,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1258,7 +1397,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="27">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1573,6 +1712,20 @@
           <color auto="1"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1767,25 +1920,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="15"/>
-      <tableStyleElement type="headerRow" dxfId="14"/>
-      <tableStyleElement type="totalRow" dxfId="13"/>
-      <tableStyleElement type="firstColumn" dxfId="12"/>
-      <tableStyleElement type="lastColumn" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="9"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="25"/>
-      <tableStyleElement type="totalRow" dxfId="24"/>
-      <tableStyleElement type="firstRowStripe" dxfId="23"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="22"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="21"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="20"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="19"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="18"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="17"/>
-      <tableStyleElement type="pageFieldValues" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="26"/>
+      <tableStyleElement type="totalRow" dxfId="25"/>
+      <tableStyleElement type="firstRowStripe" dxfId="24"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="23"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="22"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="21"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="20"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="19"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="18"/>
+      <tableStyleElement type="pageFieldValues" dxfId="17"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1797,9 +1950,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A7:I21" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A7:I21" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A7:J20" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A7:J20" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="10">
     <tableColumn id="1" name="Scenario TID" dataDxfId="0"/>
     <tableColumn id="2" name=" Scenario Desciption" dataDxfId="1"/>
     <tableColumn id="3" name="Test Case ID" dataDxfId="2"/>
@@ -1809,6 +1962,7 @@
     <tableColumn id="7" name="Actual Result" dataDxfId="6"/>
     <tableColumn id="8" name="Status" dataDxfId="7"/>
     <tableColumn id="9" name="Executed QA Name " dataDxfId="8"/>
+    <tableColumn id="10" name="Screenshots" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2014,7 +2168,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="12.6285714285714" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.8571428571429" style="10" customWidth="1"/>
@@ -2029,13 +2183,13 @@
     <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="5:6">
+    <row r="1" customHeight="1" spans="1:11">
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="11"/>
     </row>
-    <row r="2" customHeight="1" spans="5:6">
+    <row r="2" customHeight="1" spans="1:11">
       <c r="E2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2043,7 +2197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="5:6">
+    <row r="3" customHeight="1" spans="1:11">
       <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2051,7 +2205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="5:6">
+    <row r="4" customHeight="1" spans="1:11">
       <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
@@ -2059,698 +2213,695 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="5:6">
+    <row r="5" customHeight="1" spans="1:11">
       <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="7">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="5:6">
+      <c r="F5" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:11">
       <c r="E6" s="12"/>
       <c r="F6" s="13"/>
     </row>
     <row r="7" customHeight="1" spans="1:11">
       <c r="A7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" ht="57" customHeight="1" spans="1:11">
+      <c r="A8" s="16">
+        <v>1</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="26"/>
+    </row>
+    <row r="9" ht="52" customHeight="1" spans="1:11">
+      <c r="A9" s="27">
+        <v>2</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" ht="79" customHeight="1" spans="1:11">
+      <c r="A10" s="16">
+        <v>3</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="26"/>
+    </row>
+    <row r="11" ht="67" customHeight="1" spans="1:11">
+      <c r="A11" s="34">
+        <v>4</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" s="26"/>
+    </row>
+    <row r="12" ht="93" customHeight="1" spans="1:11">
+      <c r="A12" s="36">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="26"/>
+    </row>
+    <row r="13" ht="66" customHeight="1" spans="1:11">
+      <c r="A13" s="34">
+        <v>6</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="26"/>
+    </row>
+    <row r="14" ht="68" customHeight="1" spans="1:11">
+      <c r="A14" s="34">
+        <v>7</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="26"/>
+    </row>
+    <row r="15" ht="83" customHeight="1" spans="1:11">
+      <c r="A15" s="34">
         <v>8</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B15" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="K15" s="26"/>
+    </row>
+    <row r="16" ht="83" customHeight="1" spans="1:11">
+      <c r="A16" s="34">
         <v>9</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="B16" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="26"/>
+    </row>
+    <row r="17" ht="48" customHeight="1" spans="1:11">
+      <c r="A17" s="34">
         <v>10</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="B17" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="26"/>
+    </row>
+    <row r="18" ht="42" customHeight="1" spans="1:11">
+      <c r="A18" s="34">
         <v>11</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="B18" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="K18" s="26"/>
+    </row>
+    <row r="19" ht="53" customHeight="1" spans="1:11">
+      <c r="A19" s="34">
         <v>12</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="B19" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="K19" s="26"/>
+    </row>
+    <row r="20" ht="46" customHeight="1" spans="1:11">
+      <c r="A20" s="34">
         <v>13</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-    </row>
-    <row r="8" ht="57" customHeight="1" spans="1:11">
-      <c r="A8" s="14">
-        <v>1</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-    </row>
-    <row r="9" ht="52" customHeight="1" spans="1:11">
-      <c r="A9" s="21">
-        <v>2</v>
-      </c>
-      <c r="B9" s="22" t="s">
+      <c r="B20" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="H20" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="I20" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-    </row>
-    <row r="10" ht="79" customHeight="1" spans="1:11">
-      <c r="A10" s="14">
-        <v>3</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-    </row>
-    <row r="11" ht="67" customHeight="1" spans="1:11">
-      <c r="A11" s="25">
-        <v>4</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-    </row>
-    <row r="12" ht="93" customHeight="1" spans="1:11">
-      <c r="A12" s="27">
-        <v>5</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-    </row>
-    <row r="13" ht="66" customHeight="1" spans="1:11">
-      <c r="A13" s="25">
-        <v>6</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-    </row>
-    <row r="14" ht="59" customHeight="1" spans="1:11">
-      <c r="A14" s="28">
-        <v>7</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-    </row>
-    <row r="15" ht="68" customHeight="1" spans="1:11">
-      <c r="A15" s="21">
-        <v>8</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-    </row>
-    <row r="16" ht="83" customHeight="1" spans="1:11">
-      <c r="A16" s="28">
-        <v>9</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-    </row>
-    <row r="17" ht="83" customHeight="1" spans="1:11">
-      <c r="A17" s="21">
-        <v>10</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-    </row>
-    <row r="18" ht="48" customHeight="1" spans="1:11">
-      <c r="A18" s="28">
-        <v>11</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-    </row>
-    <row r="19" ht="42" customHeight="1" spans="1:11">
-      <c r="A19" s="21">
-        <v>12</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-    </row>
-    <row r="20" ht="53" customHeight="1" spans="1:11">
-      <c r="A20" s="28">
-        <v>13</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-    </row>
-    <row r="21" ht="46" customHeight="1" spans="1:11">
-      <c r="A21" s="21">
-        <v>14</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
+      <c r="J20" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="K20" s="26"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:11">
+      <c r="A21" s="48"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
     </row>
     <row r="22" customHeight="1" spans="1:11">
-      <c r="A22" s="30"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
+      <c r="A22" s="50"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
     </row>
     <row r="23" customHeight="1" spans="1:11">
-      <c r="A23" s="32"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
+      <c r="A23" s="48"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
     </row>
     <row r="24" customHeight="1" spans="1:11">
-      <c r="A24" s="30"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
+      <c r="A24" s="50"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
     </row>
     <row r="25" customHeight="1" spans="1:11">
-      <c r="A25" s="32"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
+      <c r="A25" s="48"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
     </row>
     <row r="26" customHeight="1" spans="1:11">
-      <c r="A26" s="30"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
+      <c r="A26" s="50"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
     </row>
     <row r="27" customHeight="1" spans="1:11">
-      <c r="A27" s="32"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
+      <c r="A27" s="48"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
     </row>
     <row r="28" customHeight="1" spans="1:11">
-      <c r="A28" s="30"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
+      <c r="A28" s="50"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
     </row>
     <row r="29" customHeight="1" spans="1:11">
-      <c r="A29" s="32"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="34"/>
-      <c r="K29" s="34"/>
+      <c r="A29" s="48"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
     </row>
     <row r="30" customHeight="1" spans="1:11">
-      <c r="A30" s="30"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
+      <c r="A30" s="50"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
     </row>
     <row r="31" customHeight="1" spans="1:11">
-      <c r="A31" s="32"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
+      <c r="A31" s="48"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
     </row>
     <row r="32" customHeight="1" spans="1:11">
-      <c r="A32" s="30"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
+      <c r="A32" s="50"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
     </row>
     <row r="33" customHeight="1" spans="1:11">
-      <c r="A33" s="32"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
+      <c r="A33" s="48"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
     </row>
     <row r="34" customHeight="1" spans="1:11">
-      <c r="A34" s="30"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
+      <c r="A34" s="50"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
     </row>
     <row r="35" customHeight="1" spans="1:11">
-      <c r="A35" s="32"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
+      <c r="A35" s="48"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
     </row>
     <row r="36" customHeight="1" spans="1:11">
-      <c r="A36" s="30"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
+      <c r="A36" s="50"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
     </row>
     <row r="37" customHeight="1" spans="1:11">
-      <c r="A37" s="32"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-    </row>
-    <row r="38" customHeight="1" spans="10:11">
-      <c r="J38" s="35"/>
-      <c r="K38" s="35"/>
-    </row>
-    <row r="39" customHeight="1" spans="10:11">
-      <c r="J39" s="35"/>
-      <c r="K39" s="35"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="51"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:11">
+      <c r="J38" s="51"/>
+      <c r="K38" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2760,6 +2911,18 @@
     <hyperlink ref="E8" r:id="rId2" display="1) Search https://vwo.com/           2) Click on Login &gt; VWO Login                                        3) Click on 'Start free trial'"/>
     <hyperlink ref="F8" r:id="rId3" display="You should land on https://vwo.com/free-trial/ page for registration"/>
     <hyperlink ref="G8" r:id="rId3" display="https://vwo.com/free-trial/ is opened"/>
+    <hyperlink ref="J9" r:id="rId4" display="SS02"/>
+    <hyperlink ref="J8" r:id="rId5" display="SS01"/>
+    <hyperlink ref="J10" r:id="rId6" display="SS03"/>
+    <hyperlink ref="J11" r:id="rId7" display="SS04"/>
+    <hyperlink ref="J12" r:id="rId8" display="SS05"/>
+    <hyperlink ref="J14" r:id="rId9" display="SS07"/>
+    <hyperlink ref="J15" r:id="rId9" display="SS08"/>
+    <hyperlink ref="J16" r:id="rId10" display="SS09"/>
+    <hyperlink ref="J17" r:id="rId11" display="SS10"/>
+    <hyperlink ref="J18" r:id="rId12" display="SS11"/>
+    <hyperlink ref="J19" r:id="rId13" display="SS12"/>
+    <hyperlink ref="J20" r:id="rId14" display="SS13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2786,13 +2949,13 @@
     <col min="9" max="9" width="24.7619047619048" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="5:6">
+    <row r="1" ht="15.75" customHeight="1" spans="1:9">
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="5:6">
+    <row r="2" ht="15.75" customHeight="1" spans="1:9">
       <c r="E2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2800,15 +2963,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="5:6">
+    <row r="3" ht="15.75" customHeight="1" spans="1:9">
       <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" spans="5:6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:9">
       <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
@@ -2816,7 +2979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="5:6">
+    <row r="5" ht="15.75" customHeight="1" spans="1:9">
       <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
@@ -2827,44 +2990,154 @@
     <row r="6" ht="15.75" customHeight="1"/>
     <row r="7" ht="15.75" customHeight="1" spans="1:9">
       <c r="A7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A12">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A15">
         <v>8</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A16">
         <v>9</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A17">
         <v>10</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A18">
         <v>11</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1"/>
-    <row r="9" ht="15.75" customHeight="1"/>
-    <row r="10" ht="15.75" customHeight="1"/>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="I18" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
     <row r="21" ht="15.75" customHeight="1"/>
